--- a/docs/usuarios_motor_glosas.xlsx
+++ b/docs/usuarios_motor_glosas.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Credenciales de Acceso" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Credenciales" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Guía de Uso" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Buenas prácticas IA" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -80,6 +82,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="003730A3"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001E40AF"/>
       <sz val="9"/>
     </font>
@@ -94,8 +102,50 @@
       <color rgb="00991B1B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000F172A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0010B981"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000369A1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00F59E0B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="003730A3"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -134,12 +184,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FEF2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010B981"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DC2626"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F59E0B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003730A3"/>
       </patternFill>
     </fill>
   </fills>
@@ -169,7 +244,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,11 +285,50 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,34 +695,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ESE HOSPITAL UNIVERSITARIO DE SANTANDER</t>
+          <t>IA GLOSAS SINAC SC · ESE Hospital Universitario de Santander</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Motor de Glosas — Credenciales de Acceso</t>
+          <t>Credenciales de Acceso · 29 usuarios</t>
         </is>
       </c>
     </row>
     <row r="3" ht="38" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>INSTRUCCIONES: La contraseña inicial de cada usuario corresponde al PREFIJO de su correo (parte antes del @). Por ejemplo, para glosashus04@sinacsc.com, la contraseña es 'glosashus04'. Cambie su contraseña inmediatamente después del primer ingreso.</t>
+          <t>La CONTRASEÑA INICIAL es el PREFIJO del correo (parte antes del @). Ej.: glosashus04@sinacsc.com → contraseña: glosashus04 · Cambie su contraseña en el primer ingreso.</t>
         </is>
       </c>
     </row>
@@ -695,22 +809,22 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>DIANEYDA QUINTERO</t>
+          <t>YENFERSON ORTEGA</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>glosashus11@sinacsc.com</t>
+          <t>coordinadorglosashus01@sinacsc.com</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>glosashus11</t>
+          <t>coordinadorglosashus01</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>AUDITOR</t>
+          <t>COORDINADOR</t>
         </is>
       </c>
     </row>
@@ -720,20 +834,20 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>CAROLINA CIFUENTES</t>
+          <t>DIANEYDA QUINTERO</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>glosashus02@sinacsc.com</t>
+          <t>glosashus11@sinacsc.com</t>
         </is>
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>glosashus02</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
+          <t>glosashus11</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -745,20 +859,20 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>JHON JAIMES</t>
+          <t>RUBY MILENA</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>glosashus04@sinacsc.com</t>
+          <t>carterahus04@sinacsc.com</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>glosashus04</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+          <t>carterahus04</t>
+        </is>
+      </c>
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -770,20 +884,20 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>MARICELA ROJAS</t>
+          <t>CAROLINA CIFUENTES</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>glosashus05@sinacsc.com</t>
+          <t>glosashus02@sinacsc.com</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>glosashus05</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
+          <t>glosashus02</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -795,20 +909,20 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>IRMA RIOS</t>
+          <t>JHON JAIMES</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>carterahus01@sinacsc.com</t>
+          <t>glosashus04@sinacsc.com</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>carterahus01</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
+          <t>glosashus04</t>
+        </is>
+      </c>
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -820,20 +934,20 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>RUBY MILENA</t>
+          <t>MARICELA ROJAS</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>carterahus04@sinacsc.com</t>
+          <t>glosashus05@sinacsc.com</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>carterahus04</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
+          <t>glosashus05</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -845,20 +959,20 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>PATRICIA QUIÑONES</t>
+          <t>IRMA RIOS</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>carterahus05@sinacsc.com</t>
+          <t>carterahus01@sinacsc.com</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>carterahus05</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
+          <t>carterahus01</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -870,20 +984,20 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>KAREN ORTIZ</t>
+          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>radicadevoluciones@sinacsc.com</t>
+          <t>glosashus12@sinacsc.com</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>radicadevoluciones</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
+          <t>glosashus12</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -895,20 +1009,20 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>SEBASTIAN SANCHES</t>
+          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>devoluciones01@sinacsc.com</t>
+          <t>devoluciones02@sinacsc.com</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>devoluciones01</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
+          <t>devoluciones02</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -920,20 +1034,20 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>YUDY AMAYA</t>
+          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>coordinacioncartera@hus.gov.co</t>
+          <t>glosashus10@sinacsc.com</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>coordinacioncartera</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
+          <t>glosashus10</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -945,20 +1059,20 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>CLAUDIA SUAREZ</t>
+          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>glosashus08@sinacsc.com</t>
+          <t>glosashus16@sinacsc.com</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>glosashus08</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
+          <t>glosashus16</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -970,20 +1084,20 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>YENFERSON ORTEGA</t>
+          <t>KAREN ORTIZ</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>glosashus07@sinacsc.com</t>
+          <t>radicadevoluciones@sinacsc.com</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>glosashus07</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
+          <t>radicadevoluciones</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -995,20 +1109,20 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
+          <t>YUDY AMAYA</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>glosashus12@sinacsc.com</t>
+          <t>coordinacioncartera@hus.gov.co</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>glosashus12</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
+          <t>coordinacioncartera</t>
+        </is>
+      </c>
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1020,20 +1134,20 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
+          <t>CLAUDIA SUAREZ</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>devoluciones02@sinacsc.com</t>
+          <t>glosashus08@sinacsc.com</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>devoluciones02</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
+          <t>glosashus08</t>
+        </is>
+      </c>
+      <c r="E21" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1045,20 +1159,20 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
+          <t>SOFIA ORTEGA</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>glosashus10@sinacsc.com</t>
+          <t>glosashus07@sinacsc.com</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>glosashus10</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
+          <t>glosashus07</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1070,20 +1184,20 @@
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>A_A_A_A (EQUIPO ASEGURADORAS)</t>
+          <t>PATRICIA QUIÑONES</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>glosashus16@sinacsc.com</t>
+          <t>carterahus05@sinacsc.com</t>
         </is>
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>glosashus16</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
+          <t>carterahus05</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1108,7 +1222,7 @@
           <t>auditorhus01</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1120,20 +1234,20 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>LEIDY JHOANA SANGUINO</t>
+          <t>LEYDI ZULAY GONZALEZ</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>auditorhus02@sinacsc.com</t>
+          <t>auditorhus03@sinacsc.com</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>auditorhus02</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
+          <t>auditorhus03</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1145,20 +1259,20 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>LEYDI ZULAY GONZALEZ</t>
+          <t>LEIDY JHOANA SANGUINO</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>auditorhus03@sinacsc.com</t>
+          <t>auditorhus02@sinacsc.com</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>auditorhus03</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
+          <t>auditorhus02</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1183,7 +1297,7 @@
           <t>devoluciones03</t>
         </is>
       </c>
-      <c r="E27" s="13" t="inlineStr">
+      <c r="E27" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1208,7 +1322,7 @@
           <t>devoluciones1</t>
         </is>
       </c>
-      <c r="E28" s="13" t="inlineStr">
+      <c r="E28" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
@@ -1233,33 +1347,1182 @@
           <t>glosashus03</t>
         </is>
       </c>
-      <c r="E29" s="13" t="inlineStr">
+      <c r="E29" s="14" t="inlineStr">
         <is>
           <t>AUDITOR</t>
         </is>
       </c>
     </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>SEBASTIAN SANCHES</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>devoluciones01@sinacsc.com</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>devoluciones01</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+    </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>Total de usuarios: 24  ·  URL: https://motor-glosas-hus.onrender.com  ·  Soporte: cartera@hus.gov.co</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="38" customHeight="1">
-      <c r="A33" s="15" t="inlineStr">
-        <is>
-          <t>🔒 SEGURIDAD: (1) La contraseña inicial debe cambiarse en el primer login.  (2) Activar autenticación de dos factores (2FA) desde el menú de usuario.  (3) No compartir credenciales — cada usuario tiene un registro de auditoría individual.</t>
+      <c r="A31" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>DANIEL FONCE</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>glosashus01@sinacsc.com</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>glosashus01</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>ELIAS CARVAJAL</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>glosashus15@sinacsc.com</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t>glosashus15</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>IVAN ARCINIEGAS</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>glosashus13@sinacsc.com</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>glosashus13</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>CAMILO CASTILLO</t>
+        </is>
+      </c>
+      <c r="C34" s="7" t="inlineStr">
+        <is>
+          <t>glosashus14@sinacsc.com</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>glosashus14</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>AUDITOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="15" t="inlineStr">
+        <is>
+          <t>Total usuarios: 29   ·   URL: https://motor-glosas-hus.onrender.com   ·   Soporte: cartera@hus.gov.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="38" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>🔒 SEGURIDAD: (1) La contraseña inicial DEBE cambiarse en el primer login.  (2) Activar 2FA desde el menú de usuario si maneja datos sensibles.  (3) NO compartir credenciales — cada acción queda en el registro de auditoría individual.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A33:E33"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A38:E38"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IA GLOSAS SINAC SC · ESE Hospital Universitario de Santander</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Guía de Ingreso y Uso de la IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Lea esta guía antes del primer uso. Tiempo estimado: 5 minutos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>🔐 1. INGRESAR AL SISTEMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>https://motor-glosas-hus.onrender.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>Correo</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>El que aparece en la hoja 'Credenciales'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Contraseña</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Prefijo del correo (ej. glosashus04@sinacsc.com → glosashus04).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Primer login</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>El sistema le pide cambiar la contraseña. Use una segura (8+ caracteres, números, símbolos).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
+        <is>
+          <t>Problemas</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Si ve pantalla en blanco, visite /reset-sw.html y vuelva a entrar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>⚖️ 2. ANALIZAR UNA GLOSA INDIVIDUAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>Paso 1</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Panel 'Analizar glosa' (menú lateral izquierdo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>Paso 2</t>
+        </is>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>Seleccionar EPS / Pagador del desplegable. Si no aparece, elija 'OTRA / SIN DEFINIR'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
+        <is>
+          <t>Paso 3</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Pegar el NÚMERO DE FACTURA. El sistema buscará conceptos ya cargados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Paso 4</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>Si aparece la caja azul con los conceptos, haga click en el que desea responder. El texto se autocompleta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>Paso 5</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Elegir etapa (RESPUESTA A GLOSA / RATIFICADA / ACLARACIÓN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="18" t="inlineStr">
+        <is>
+          <t>Paso 6</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>Tono: Conciliador para Salud Total/EPS confiables; Firme para cuando hay que exigir pago.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>Paso 7</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>Subir soportes PDF (opcional, hasta 10 archivos de 15MB).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>Paso 8</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>Click en ANALIZAR. La IA demora 10-30 segundos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>📥 3. IMPORTAR RECEPCIÓN (Excel 4 hojas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>Menú lateral → 'Importar recepción'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="18" t="inlineStr">
+        <is>
+          <t>Formato</t>
+        </is>
+      </c>
+      <c r="B24" s="19" t="inlineStr">
+        <is>
+          <t>Excel (.xlsx) con 4 hojas: INICIAL, RATIFICADA, I, R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="34" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Qué hace</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>Crea las glosas automáticamente, las asigna a cada gestor, carga todos los conceptos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="34" customHeight="1">
+      <c r="A26" s="18" t="inlineStr">
+        <is>
+          <t>Después</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Cada gestor las ve en su bandeja 'Mis glosas'. Los conceptos aparecen al buscar la factura en Analizar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>📋 4. IMPORTACIÓN MASIVA (copy-paste Excel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="18" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Menú lateral → 'Importación masiva'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="18" t="inlineStr">
+        <is>
+          <t>Cuándo usar</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Cuando tiene varias glosas en Excel y quiere procesar de golpe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>Separador</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Tab o pipe (|) — auto-detectado. Pegue directo desde Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="34" customHeight="1">
+      <c r="A32" s="18" t="inlineStr">
+        <is>
+          <t>Columnas</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>ENTIDAD | FACTURA | VALOR | CÓDIGO | CONCEPTO | CUPS | SERVICIO | MOTIVO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>💚 5. SALUD TOTAL (archivo TXT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="18" t="inlineStr">
+        <is>
+          <t>Dónde</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Menú lateral → 'Salud Total'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
+        <is>
+          <t>Archivo</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>TXT separado por TAB o pipe con 24 columnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
+        <is>
+          <t>Tipo respuesta</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Extemporánea (fuera de términos) / Ratificada / IA (análisis completo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="34" customHeight="1">
+      <c r="A38" s="18" t="inlineStr">
+        <is>
+          <t>Resultado</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>Descarga un TXT formateado listo para radicar en el portal de Salud Total EPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>🔍 6. ATAJOS ÚTILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="18" t="inlineStr">
+        <is>
+          <t>Cmd + K (Ctrl + K)</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Spotlight: busca glosas, usuarios, EPS, contratos o abre cualquier sección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="34" customHeight="1">
+      <c r="A42" s="18" t="inlineStr">
+        <is>
+          <t>Mis glosas</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Sus glosas asignadas con semáforo de vencimiento (verde/amarillo/rojo/negro).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="18" t="inlineStr">
+        <is>
+          <t>Historial</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Todas las glosas procesadas (filtro por EPS, fecha, código).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Alertas</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Glosas próximas a vencer (según días hábiles desde recepción).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1">
+      <c r="A45" s="18" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>KPIs del mes y tendencias de 6 meses (solo COORDINADOR/SUPER_ADMIN).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>📄 7. DESCARGAR PDF DEL DICTAMEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>Después de analizar</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Botón 'Imprimir PDF' en el resultado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="18" t="inlineStr">
+        <is>
+          <t>Contenido</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>Cabecera institucional, tabla de códigos, argumento jurídico, mensaje de tiempo, firmas, pie de página SINAC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
+        <is>
+          <t>Para radicar</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>Firme manualmente el PDF impreso y adjunte al radicado en la EPS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IA GLOSAS SINAC SC · ESE Hospital Universitario de Santander</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Recomendaciones para el Equipo · Uso eficiente de la IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="38" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Seguir estas prácticas evita costos altos, respuestas genéricas y spam en el sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>✅ QUÉ SÍ HACER</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>Usar el autocompletado de factura: al pegar el número, el sistema trae los conceptos ya cargados — evita redigitar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Seleccionar el concepto específico antes de analizar (no dejar el texto genérico 'glosa objetada por la entidad pagadora').</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>Elegir el tono correcto: Firme solo cuando la EPS ya rechazó una vez; Conciliador en primera vuelta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Revisar el dictamen antes de radicar — la IA puede equivocarse en detalles; usted firma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>Subir TODOS los soportes PDF relevantes (historia clínica, autorización, RIPS) al analizar. La IA los usa como contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Usar 'Refinar' en el modal cuando quiera ajustar tono o cita de una norma específica — no re-analizar desde cero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="32" customHeight="1">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>Guardar argumentos ganadores como 'Plantilla Gold' (⭐): la IA los usa de ejemplo en casos similares futuros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="32" customHeight="1">
+      <c r="A13" s="21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Agrupar glosas por factura y usar 'Analizar todos' en vez de ir una por una — más rápido y consistente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>❌ QUÉ NO HACER</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="32" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>NO analizar la misma glosa múltiples veces seguidas para 'probar' respuestas. Cada clic cuesta tokens y queda en auditoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="32" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>NO pegar textos inútiles (ej. 'hola', '123', 'test', solo el código glosa TA0801 sin contexto). La IA genera respuesta mala.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="32" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B18" s="19" t="inlineStr">
+        <is>
+          <t>NO subir PDFs de 15MB si solo necesita 2-3 páginas. Comprímalos antes (ILovePDF, Smallpdf).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>NO usar el sistema desde 5 pestañas a la vez — se pisan las sesiones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B20" s="19" t="inlineStr">
+        <is>
+          <t>NO spamear el botón Analizar si tarda — la primera petición ya está en curso. Espere la respuesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="32" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>NO modificar manualmente el dictamen para borrar citas legales. La IA calibra normativa; si quiere otra cita, use 'Refinar'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="19" t="inlineStr">
+        <is>
+          <t>NO compartir credenciales con compañeros. Cada acción queda registrada al dueño del correo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="32" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>NO usar glosas ajenas para 'aprender'. Cada auditor ve las suyas; el COORDINADOR ve todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>📈 PARA RESPUESTAS DE MEJOR CALIDAD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="32" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>Dé contexto: Número de factura + Código glosa + Servicio + Valor. La IA rinde 3× mejor con datos completos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="32" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>Si la EPS escribió una OBSERVACIÓN específica (ej. 'no concuerda cantidad facturada'), péguela completa. Ahí está la clave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="32" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>Para glosas ratificadas use el tono Firme + cite la Ley 1438 Art. 57 y exija mesa de conciliación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="32" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>Para glosas extemporáneas, la IA detecta automáticamente si superan 20 días hábiles y responde con plantilla RE9502.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="32" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>Si el dictamen cita una norma derogada o incorrecta (raro), use 'Validar' ✅ en el modal — el sistema detecta automáticamente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>⚡ USO RESPONSABLE DE TOKENS IA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>Cada análisis = ~2000-4000 tokens = costo real. Un uso responsable beneficia a todo el equipo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Lote grande (50+ conceptos)? Usar 'Analizar todos' con pausa automática entre llamadas (rate-limit interno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Antes de analizar, revise si la glosa YA tiene dictamen en Historial. No duplicar trabajo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Si necesita re-generar, use 'Regenerar' — mantiene contexto; NO borrar y analizar de nuevo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>Horarios de menor carga (8–11 am) responden más rápido que horarios punta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>🆘 SI ALGO NO FUNCIONA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>Pantalla en blanco al entrar → visite /reset-sw.html y recargue con Ctrl+Shift+R.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="32" customHeight="1">
+      <c r="A41" s="28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Mensaje 500 o 'Error interno' → intente de nuevo en 1-2 min; si persiste, reporte al COORDINADOR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="32" customHeight="1">
+      <c r="A42" s="28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Import masiva falla → verifique que el archivo Excel tenga las 4 hojas con los encabezados correctos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="32" customHeight="1">
+      <c r="A43" s="28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Contraseña olvidada → el SUPER_ADMIN (YESID o Auditor Principal) puede resetearla en el panel Usuarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="22" customHeight="1">
+      <c r="A44" s="28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Sugerencias de mejora → anotarlas y enviarlas al COORDINADOR (YENFERSON ORTEGA).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="39">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="B35:F35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
